--- a/sampledata/7tntmainchart.xlsx
+++ b/sampledata/7tntmainchart.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\RLLT\Webapp\sampledata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86419EF5-9F29-4477-812C-EB6B84740A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECFC7076-B74C-44EF-94A9-8C13DD0A86BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="74">
   <si>
     <t>Day</t>
   </si>
@@ -250,6 +250,10 @@
   </si>
   <si>
     <t>389</t>
+  </si>
+  <si>
+    <t>Verse: Genesis 1:1
+Text: “In the beginning God created the heaven and the earth.”</t>
   </si>
 </sst>
 </file>
@@ -317,19 +321,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -615,12 +618,10 @@
   <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="4"/>
-    <col min="2" max="2" width="23.5546875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="64.44140625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="17.109375" style="6" customWidth="1"/>
-    <col min="5" max="5" width="10.77734375" style="6" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="4"/>
+    <col min="2" max="2" width="23.5546875" customWidth="1"/>
+    <col min="3" max="3" width="64.44140625" customWidth="1"/>
+    <col min="4" max="4" width="17.109375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="10.77734375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -647,692 +648,692 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="4">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" s="5">
+        <v>1</v>
+      </c>
+      <c r="E2" s="5">
+        <v>10</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" s="6">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" s="6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="6">
-        <v>1</v>
-      </c>
-      <c r="E2" s="6">
+      <c r="D8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" s="6">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" s="6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="F2" s="4">
-        <v>1</v>
-      </c>
-      <c r="G2" s="7">
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" s="6">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" s="6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13" s="6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14" s="6">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="4">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
+    <row r="15" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D15" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15" s="6">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16" s="6">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18" s="6">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20">
         <v>19</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="B20" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20" s="6">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21">
         <v>20</v>
       </c>
-      <c r="F3" s="4">
-        <v>1</v>
-      </c>
-      <c r="G3" s="7">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="B21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21" s="6">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C22" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="6" t="s">
+      <c r="D22" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22" s="6">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A23">
         <v>22</v>
       </c>
-      <c r="F4" s="4">
-        <v>1</v>
-      </c>
-      <c r="G4" s="7">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="B23" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C23" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D23" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A24">
         <v>23</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="B24" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24" s="6">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25">
         <v>24</v>
       </c>
-      <c r="F5" s="4">
-        <v>1</v>
-      </c>
-      <c r="G5" s="7">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
+      <c r="B25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="6" t="s">
+      <c r="C26" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26" s="6">
         <v>27</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" s="4">
-        <v>1</v>
-      </c>
-      <c r="G6" s="7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="4">
+    </row>
+    <row r="27" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="4">
-        <v>1</v>
-      </c>
-      <c r="G7" s="7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="4">
+      <c r="C27" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" s="4">
-        <v>1</v>
-      </c>
-      <c r="G8" s="7">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
+      <c r="D27" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27" s="6">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" s="4">
-        <v>1</v>
-      </c>
-      <c r="G9" s="7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="4">
-        <v>9</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" s="4">
-        <v>1</v>
-      </c>
-      <c r="G10" s="7">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="4">
-        <v>10</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" s="4">
-        <v>1</v>
-      </c>
-      <c r="G11" s="7">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="4">
-        <v>11</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" s="4">
-        <v>1</v>
-      </c>
-      <c r="G12" s="7">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="4">
-        <v>12</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="F13" s="4">
-        <v>1</v>
-      </c>
-      <c r="G13" s="7">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="4">
-        <v>13</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F14" s="4">
-        <v>1</v>
-      </c>
-      <c r="G14" s="7">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="4">
-        <v>14</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15" s="4">
-        <v>1</v>
-      </c>
-      <c r="G15" s="7">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>15</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F16" s="4">
-        <v>1</v>
-      </c>
-      <c r="G16" s="7">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>16</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="F17" s="4">
-        <v>1</v>
-      </c>
-      <c r="G17" s="7">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>17</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="F18" s="4">
-        <v>1</v>
-      </c>
-      <c r="G18" s="7">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="4">
-        <v>18</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="F19" s="4">
-        <v>1</v>
-      </c>
-      <c r="G19" s="7">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="4">
-        <v>19</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="F20" s="4">
-        <v>1</v>
-      </c>
-      <c r="G20" s="7">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>20</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="F21" s="4">
-        <v>1</v>
-      </c>
-      <c r="G21" s="7">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="4">
-        <v>21</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="F22" s="4">
-        <v>1</v>
-      </c>
-      <c r="G22" s="7">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A23" s="4">
-        <v>22</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F23" s="4">
-        <v>1</v>
-      </c>
-      <c r="G23" s="7">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="4">
-        <v>23</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="F24" s="4">
-        <v>1</v>
-      </c>
-      <c r="G24" s="7">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="4">
-        <v>24</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="F25" s="4">
-        <v>1</v>
-      </c>
-      <c r="G25" s="7">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="4">
-        <v>25</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="F26" s="4">
-        <v>1</v>
-      </c>
-      <c r="G26" s="7">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="4">
-        <v>26</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="F27" s="4">
-        <v>1</v>
-      </c>
-      <c r="G27" s="7">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="4">
-        <v>27</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D28" s="1">
         <v>331</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F28" s="4">
-        <v>1</v>
-      </c>
-      <c r="G28" s="7">
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28" s="6">
         <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A29" s="4">
+      <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" t="s">
         <v>10</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D29" s="1">
         <v>339</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E29" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="F29" s="4">
-        <v>1</v>
-      </c>
-      <c r="G29" s="7">
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29" s="6">
         <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A30" s="4">
+      <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="4" t="s">
         <v>15</v>
       </c>
       <c r="D30" s="1">
         <v>357</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="F30" s="4">
-        <v>1</v>
-      </c>
-      <c r="G30" s="7">
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30" s="6">
         <v>37</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="4">
+      <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D31" s="1">
         <v>371</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E31" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="F31" s="4">
-        <v>1</v>
-      </c>
-      <c r="G31" s="7">
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31" s="6">
         <v>34</v>
       </c>
     </row>
